--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5284,10 +5284,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>54468359</v>
+        <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>101326</v>
+        <v>106494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5295,34 +5295,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stortjäran NO 650 m, Upl</t>
+          <t>Stortjärans gård N om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>683660</v>
+        <v>683359</v>
       </c>
       <c r="R43" t="n">
-        <v>6627234</v>
+        <v>6627686</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5344,17 +5351,22 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Rimbo</t>
+          <t>Fasterna</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En vinterståndare. Ca fem plantor.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5363,35 +5375,36 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Örtrik gammal barrskog.</t>
+          <t>Fuktig granskog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson, Karin Hendahl, Lena Öberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54468359</t>
+          <t>https://artportalen.se/Sighting/136882009</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121408368</v>
+        <v>54468359</v>
       </c>
       <c r="B44" t="n">
         <v>101326</v>
@@ -5422,14 +5435,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stortjärans NR, Upl</t>
+          <t>Stortjäran NO 650 m, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>683297</v>
+        <v>683660</v>
       </c>
       <c r="R44" t="n">
-        <v>6627452</v>
+        <v>6627234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5451,17 +5464,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Fasterna</t>
+          <t>Rimbo</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2015-07-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2015-07-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5472,32 +5485,33 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Örtrik gammal barrskog.</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121408368</t>
+          <t>https://artportalen.se/Sighting/54468359</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121408369</v>
+        <v>121408368</v>
       </c>
       <c r="B45" t="n">
         <v>101326</v>
@@ -5532,10 +5546,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>683240</v>
+        <v>683297</v>
       </c>
       <c r="R45" t="n">
-        <v>6627295</v>
+        <v>6627452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5597,16 +5611,16 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121408369</t>
+          <t>https://artportalen.se/Sighting/121408368</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>54468355</v>
+        <v>121408369</v>
       </c>
       <c r="B46" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5614,34 +5628,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stortjäran NO 650 m, Upl</t>
+          <t>Stortjärans NR, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683660</v>
+        <v>683240</v>
       </c>
       <c r="R46" t="n">
-        <v>6627234</v>
+        <v>6627295</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5663,17 +5677,17 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Rimbo</t>
+          <t>Fasterna</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5684,72 +5698,73 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Örtrik gammal barrskog.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54468355</t>
+          <t>https://artportalen.se/Sighting/121408369</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126537074</v>
+        <v>54468355</v>
       </c>
       <c r="B47" t="n">
-        <v>80657</v>
+        <v>101228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228430</v>
+        <v>222771</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Utanför stortjärans NR, Upl</t>
+          <t>Stortjäran NO 650 m, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683688</v>
+        <v>683660</v>
       </c>
       <c r="R47" t="n">
-        <v>6627236</v>
+        <v>6627234</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5773,12 +5788,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2015-07-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2015-07-13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5787,23 +5802,128 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Örtrik gammal barrskog.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54468355</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126537074</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80657</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Utanför stortjärans NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>683688</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6627236</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Carin von Köhler, Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126537074</t>
         </is>
@@ -5857,6 +5977,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5313,11 +5313,7 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 8557-2021 artfynd.xlsx
+++ b/artfynd/S 8557-2021 artfynd.xlsx
@@ -5287,7 +5287,7 @@
         <v>136882009</v>
       </c>
       <c r="B43" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
